--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260807_005415.xlsx
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
